--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/Dungeon.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/Dungeon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5542FB3-D6A5-4307-B1FB-3DB760D5F070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EECDD933-EE35-4E89-99A7-3A76BCF9B266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="5040" windowWidth="51320" windowHeight="15840" xr2:uid="{08FD8797-AF4E-4C4F-BF22-C35A03C81A54}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -98,28 +98,51 @@
     <t>同一区域内的排序</t>
   </si>
   <si>
+    <t>PosX</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>格子在副本界面里的位置X-UI坐标-相对Contents中心-用副本摆位窗口拖</t>
+  </si>
+  <si>
+    <t>PosY</t>
+  </si>
+  <si>
+    <t>格子在副本界面里的位置Y-UI坐标-同上</t>
+  </si>
+  <si>
     <t>密林入口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Assets/AddressableAssets/Remote/Texture2D/Dungeon/dungeon_thumbnail_31005.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>迷雾小径</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Assets/AddressableAssets/Remote/Texture2D/Dungeon/dungeon_thumbnail_31006.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>古树之下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Assets/AddressableAssets/Remote/Texture2D/Dungeon/dungeon_thumbnail_31007.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>密林深处</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Assets/AddressableAssets/Remote/Texture2D/Dungeon/dungeon_thumbnail_31008.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -504,10 +527,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02224BE6-0D99-4F25-AC9D-E5605B0F1108}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -529,8 +552,14 @@
       <c r="G1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -552,8 +581,14 @@
       <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="H2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -575,8 +610,14 @@
       <c r="G3" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -598,8 +639,14 @@
       <c r="G4" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="H4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>31005</v>
       </c>
@@ -607,10 +654,10 @@
         <v>31001</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -618,8 +665,14 @@
       <c r="G5">
         <v>1</v>
       </c>
+      <c r="H5" s="1">
+        <v>-576</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B6">
         <v>31006</v>
       </c>
@@ -627,10 +680,10 @@
         <v>31001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F6">
         <v>6</v>
@@ -638,8 +691,14 @@
       <c r="G6">
         <v>2</v>
       </c>
+      <c r="H6" s="1">
+        <v>-192</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B7">
         <v>31007</v>
       </c>
@@ -647,10 +706,10 @@
         <v>31001</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -658,8 +717,14 @@
       <c r="G7">
         <v>3</v>
       </c>
+      <c r="H7" s="1">
+        <v>192</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>31008</v>
       </c>
@@ -667,16 +732,22 @@
         <v>31001</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8">
         <v>4</v>
+      </c>
+      <c r="H8" s="1">
+        <v>576</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/Dungeon.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/Dungeon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EECDD933-EE35-4E89-99A7-3A76BCF9B266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{037844B0-7E16-42C5-AE8C-B0B6AD713CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5040" windowWidth="51320" windowHeight="15840" xr2:uid="{08FD8797-AF4E-4C4F-BF22-C35A03C81A54}"/>
+    <workbookView xWindow="1780" yWindow="3860" windowWidth="31070" windowHeight="14950" xr2:uid="{08FD8797-AF4E-4C4F-BF22-C35A03C81A54}"/>
   </bookViews>
   <sheets>
     <sheet name="Dungeon" sheetId="1" r:id="rId1"/>
@@ -666,10 +666,10 @@
         <v>1</v>
       </c>
       <c r="H5" s="1">
-        <v>-576</v>
+        <v>-687</v>
       </c>
       <c r="I5" s="1">
-        <v>0</v>
+        <v>-214</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -692,10 +692,10 @@
         <v>2</v>
       </c>
       <c r="H6" s="1">
-        <v>-192</v>
+        <v>684</v>
       </c>
       <c r="I6" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -718,10 +718,10 @@
         <v>3</v>
       </c>
       <c r="H7" s="1">
-        <v>192</v>
+        <v>691</v>
       </c>
       <c r="I7" s="1">
-        <v>0</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -744,10 +744,10 @@
         <v>4</v>
       </c>
       <c r="H8" s="1">
-        <v>576</v>
+        <v>-271</v>
       </c>
       <c r="I8" s="1">
-        <v>0</v>
+        <v>-206</v>
       </c>
     </row>
   </sheetData>
